--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>listed-building-grade-known</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Listed building grade known</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3880,12 +3880,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Set to true if the applicant knows the listed building grade. Set to false if they do not know it.</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3920,17 +3920,17 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3960,12 +3960,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -3975,29 +3975,21 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4008,23 +4000,31 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -4032,36 +4032,28 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4090,12 +4082,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4104,17 +4096,17 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4130,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4152,7 +4144,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4186,12 +4178,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4200,12 +4192,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4224,23 +4216,31 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>materials-not-known</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4264,36 +4264,28 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4303,45 +4295,45 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4351,8 +4343,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -4360,49 +4360,33 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>lbc-owners</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4436,19 +4420,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4458,7 +4442,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4492,19 +4476,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4548,27 +4532,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>contact-address</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Contact address</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4622,17 +4598,17 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4642,7 +4618,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4686,17 +4662,17 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>uprn</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>UPRN</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Number for a property</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4730,26 +4706,42 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -4768,28 +4760,36 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
+          <t>Ownership certificate type</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4824,12 +4824,12 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4848,31 +4848,23 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -4882,7 +4874,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4898,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>publication-date</t>
+          <t>newspaper-name</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Publication date</t>
+          <t>Newspaper name</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4920,12 +4912,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4944,28 +4936,36 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr"/>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -5000,12 +5000,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -5040,12 +5040,12 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -5055,29 +5055,21 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5088,12 +5080,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5103,8 +5095,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -5112,12 +5112,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Planning officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5128,17 +5128,17 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5168,7 +5168,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5208,12 +5208,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5248,12 +5248,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5263,29 +5263,21 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5296,7 +5288,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -5306,13 +5298,21 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -5320,12 +5320,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5336,12 +5336,12 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -5376,17 +5376,17 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -5416,17 +5416,17 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -5456,44 +5456,36 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>related-applications</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>has-related-applications</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -5504,23 +5496,31 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Details of any other development proposals made for the site</t>
@@ -5528,36 +5528,28 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5586,12 +5578,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5600,7 +5592,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5634,12 +5626,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5648,54 +5640,46 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>geometry</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5704,23 +5688,31 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>A polygon or multipolygon boundary</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>multipolygon</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
-      <c r="B107" s="2" t="n"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5738,34 +5730,26 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>site-address</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Site address</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site boundary</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Text representation of an address or site</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -5804,19 +5788,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Postcode for a contact address or site</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5826,7 +5810,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5860,19 +5844,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -5916,19 +5900,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>usrns</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>USRNs[]</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5962,26 +5946,34 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -6010,12 +6002,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6024,7 +6016,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6058,12 +6050,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
@@ -6072,12 +6064,12 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -6106,12 +6098,12 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -6120,71 +6112,79 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>site-locations</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="N114" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>can-be-seen-from</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -6208,12 +6208,12 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -6248,17 +6248,17 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6272,31 +6272,23 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -6306,7 +6298,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6322,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6344,7 +6336,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -6378,12 +6370,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -6392,15 +6384,63 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="M121" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="N121" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6408,46 +6448,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A71:A77"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B115:B120"/>
+    <mergeCell ref="B107:B115"/>
+    <mergeCell ref="A103:A106"/>
     <mergeCell ref="A44"/>
     <mergeCell ref="B37:B43"/>
-    <mergeCell ref="A97:A101"/>
     <mergeCell ref="B53:B61"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B77:B91"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="A78:A92"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="A64:A66"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="B24:B32"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A106:A114"/>
+    <mergeCell ref="A93:A97"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="A53:A61"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B78:B92"/>
+    <mergeCell ref="B116:B121"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A98:A102"/>
     <mergeCell ref="B33:B36"/>
     <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A116:A121"/>
     <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B93:B97"/>
     <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B106:B114"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="B71:B77"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="B44"/>
-    <mergeCell ref="B70:B76"/>
+    <mergeCell ref="A107:A115"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A77:A91"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A115:A120"/>
+    <mergeCell ref="B98:B102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
